--- a/backend/data/financials_by_company/0286.HK.xlsx
+++ b/backend/data/financials_by_company/0286.HK.xlsx
@@ -672,148 +672,152 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-449750</v>
+        <v>20985370</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
+        <v>0.349</v>
       </c>
       <c r="D2" t="n">
-        <v>64134000</v>
+        <v>205085000</v>
       </c>
       <c r="E2" t="n">
-        <v>-1799000</v>
+        <v>60130000</v>
       </c>
       <c r="F2" t="n">
-        <v>-1799000</v>
+        <v>60130000</v>
       </c>
       <c r="G2" t="n">
-        <v>-177421000</v>
+        <v>5300000</v>
       </c>
       <c r="H2" t="n">
-        <v>179154000</v>
+        <v>146136000</v>
       </c>
       <c r="I2" t="n">
-        <v>433549000</v>
+        <v>437161000</v>
       </c>
       <c r="J2" t="n">
-        <v>62335000</v>
+        <v>265215000</v>
       </c>
       <c r="K2" t="n">
-        <v>-116819000</v>
+        <v>119079000</v>
       </c>
       <c r="L2" t="n">
-        <v>-43941000</v>
+        <v>-57863000</v>
       </c>
       <c r="M2" t="n">
-        <v>46950000</v>
+        <v>65670000</v>
       </c>
       <c r="N2" t="n">
-        <v>9827000</v>
+        <v>7807000</v>
       </c>
       <c r="O2" t="n">
-        <v>-176071750</v>
+        <v>-33844630</v>
       </c>
       <c r="P2" t="n">
-        <v>-177421000</v>
+        <v>5300000</v>
       </c>
       <c r="Q2" t="n">
-        <v>688199000</v>
+        <v>603484000</v>
       </c>
       <c r="R2" t="n">
-        <v>-106113000</v>
+        <v>60711000</v>
       </c>
       <c r="S2" t="n">
-        <v>125506759</v>
+        <v>117287163</v>
       </c>
       <c r="T2" t="n">
-        <v>125506759</v>
+        <v>117277067</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.4144</v>
+        <v>0.045067</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.4144</v>
+        <v>0.045067</v>
       </c>
       <c r="W2" t="n">
-        <v>-177421000</v>
+        <v>5300000</v>
       </c>
       <c r="X2" t="n">
-        <v>-177421000</v>
+        <v>5300000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-177421000</v>
+        <v>5300000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-573000</v>
+        <v>-29485000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-176848000</v>
+        <v>34785000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-176848000</v>
+        <v>34785000</v>
       </c>
       <c r="AD2" t="n">
-        <v>13079000</v>
+        <v>18624000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-163769000</v>
+        <v>53409000</v>
       </c>
       <c r="AF2" t="n">
-        <v>15284000</v>
+        <v>12394000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1961000</v>
+        <v>58368000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1961000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
+        <v>-60439000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>2071000</v>
+      </c>
       <c r="AL2" t="n">
-        <v>-43941000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>6818000</v>
-      </c>
+        <v>-57863000</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>46950000</v>
+        <v>65670000</v>
       </c>
       <c r="AO2" t="n">
-        <v>9827000</v>
+        <v>7807000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-133618000</v>
+        <v>39089000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>254650000</v>
+        <v>166323000</v>
       </c>
       <c r="AR2" t="n">
-        <v>257186000</v>
+        <v>170900000</v>
       </c>
       <c r="AS2" t="n">
-        <v>116266000</v>
+        <v>107479000</v>
       </c>
       <c r="AT2" t="n">
-        <v>140920000</v>
+        <v>63421000</v>
       </c>
       <c r="AU2" t="n">
-        <v>121032000</v>
+        <v>205412000</v>
       </c>
       <c r="AV2" t="n">
-        <v>433549000</v>
+        <v>437161000</v>
       </c>
       <c r="AW2" t="n">
-        <v>554581000</v>
+        <v>642573000</v>
       </c>
       <c r="AX2" t="n">
-        <v>554581000</v>
+        <v>642573000</v>
       </c>
     </row>
     <row r="3">
@@ -964,152 +968,148 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>20985370</v>
+        <v>-449750</v>
       </c>
       <c r="C4" t="n">
-        <v>0.349</v>
+        <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>205085000</v>
+        <v>64134000</v>
       </c>
       <c r="E4" t="n">
-        <v>60130000</v>
+        <v>-1799000</v>
       </c>
       <c r="F4" t="n">
-        <v>60130000</v>
+        <v>-1799000</v>
       </c>
       <c r="G4" t="n">
-        <v>5300000</v>
+        <v>-177421000</v>
       </c>
       <c r="H4" t="n">
-        <v>146136000</v>
+        <v>179154000</v>
       </c>
       <c r="I4" t="n">
-        <v>437161000</v>
+        <v>433549000</v>
       </c>
       <c r="J4" t="n">
-        <v>265215000</v>
+        <v>62335000</v>
       </c>
       <c r="K4" t="n">
-        <v>119079000</v>
+        <v>-116819000</v>
       </c>
       <c r="L4" t="n">
-        <v>-57863000</v>
+        <v>-43941000</v>
       </c>
       <c r="M4" t="n">
-        <v>65670000</v>
+        <v>46950000</v>
       </c>
       <c r="N4" t="n">
-        <v>7807000</v>
+        <v>9827000</v>
       </c>
       <c r="O4" t="n">
-        <v>-33844630</v>
+        <v>-176071750</v>
       </c>
       <c r="P4" t="n">
-        <v>5300000</v>
+        <v>-177421000</v>
       </c>
       <c r="Q4" t="n">
-        <v>603484000</v>
+        <v>688199000</v>
       </c>
       <c r="R4" t="n">
-        <v>60711000</v>
+        <v>-106113000</v>
       </c>
       <c r="S4" t="n">
-        <v>117287163</v>
+        <v>125506759</v>
       </c>
       <c r="T4" t="n">
-        <v>117277067</v>
+        <v>125506759</v>
       </c>
       <c r="U4" t="n">
-        <v>0.045067</v>
+        <v>-1.4144</v>
       </c>
       <c r="V4" t="n">
-        <v>0.045067</v>
+        <v>-1.4144</v>
       </c>
       <c r="W4" t="n">
-        <v>5300000</v>
+        <v>-177421000</v>
       </c>
       <c r="X4" t="n">
-        <v>5300000</v>
+        <v>-177421000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5300000</v>
+        <v>-177421000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-29485000</v>
+        <v>-573000</v>
       </c>
       <c r="AB4" t="n">
-        <v>34785000</v>
+        <v>-176848000</v>
       </c>
       <c r="AC4" t="n">
-        <v>34785000</v>
+        <v>-176848000</v>
       </c>
       <c r="AD4" t="n">
-        <v>18624000</v>
+        <v>13079000</v>
       </c>
       <c r="AE4" t="n">
-        <v>53409000</v>
+        <v>-163769000</v>
       </c>
       <c r="AF4" t="n">
-        <v>12394000</v>
+        <v>15284000</v>
       </c>
       <c r="AG4" t="n">
-        <v>58368000</v>
+        <v>1961000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-60439000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2071000</v>
-      </c>
+        <v>-1961000</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>-57863000</v>
-      </c>
-      <c r="AM4" t="inlineStr"/>
+        <v>-43941000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>6818000</v>
+      </c>
       <c r="AN4" t="n">
-        <v>65670000</v>
+        <v>46950000</v>
       </c>
       <c r="AO4" t="n">
-        <v>7807000</v>
+        <v>9827000</v>
       </c>
       <c r="AP4" t="n">
-        <v>39089000</v>
+        <v>-133618000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>166323000</v>
+        <v>254650000</v>
       </c>
       <c r="AR4" t="n">
-        <v>170900000</v>
+        <v>257186000</v>
       </c>
       <c r="AS4" t="n">
-        <v>107479000</v>
+        <v>116266000</v>
       </c>
       <c r="AT4" t="n">
-        <v>63421000</v>
+        <v>140920000</v>
       </c>
       <c r="AU4" t="n">
-        <v>205412000</v>
+        <v>121032000</v>
       </c>
       <c r="AV4" t="n">
-        <v>437161000</v>
+        <v>433549000</v>
       </c>
       <c r="AW4" t="n">
-        <v>642573000</v>
+        <v>554581000</v>
       </c>
       <c r="AX4" t="n">
-        <v>642573000</v>
+        <v>554581000</v>
       </c>
     </row>
   </sheetData>
@@ -1450,187 +1450,195 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>127933124</v>
+        <v>123606201</v>
       </c>
       <c r="C2" t="n">
-        <v>127933124</v>
+        <v>123606201</v>
       </c>
       <c r="D2" t="n">
-        <v>311053000</v>
+        <v>779564000</v>
       </c>
       <c r="E2" t="n">
-        <v>614215000</v>
+        <v>1286527000</v>
       </c>
       <c r="F2" t="n">
-        <v>-390748000</v>
+        <v>-144426000</v>
       </c>
       <c r="G2" t="n">
-        <v>1129058000</v>
+        <v>1963904000</v>
       </c>
       <c r="H2" t="n">
-        <v>62471000</v>
+        <v>616988000</v>
       </c>
       <c r="I2" t="n">
-        <v>-390748000</v>
+        <v>-144426000</v>
       </c>
       <c r="J2" t="n">
-        <v>222859000</v>
+        <v>419336000</v>
       </c>
       <c r="K2" t="n">
-        <v>737702000</v>
+        <v>1096713000</v>
       </c>
       <c r="L2" t="n">
-        <v>1048369000</v>
+        <v>1822383000</v>
       </c>
       <c r="M2" t="n">
-        <v>755949000</v>
+        <v>1249743000</v>
       </c>
       <c r="N2" t="n">
-        <v>18247000</v>
+        <v>153030000</v>
       </c>
       <c r="O2" t="n">
-        <v>737702000</v>
+        <v>1096713000</v>
       </c>
       <c r="P2" t="n">
-        <v>44350000</v>
+        <v>42850000</v>
       </c>
       <c r="Q2" t="n">
-        <v>44350000</v>
+        <v>42850000</v>
       </c>
       <c r="R2" t="n">
-        <v>1204218000</v>
+        <v>1773206000</v>
       </c>
       <c r="S2" t="n">
-        <v>819790000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>224189000</v>
-      </c>
+        <v>1174336000</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>152817000</v>
+        <v>167524000</v>
       </c>
       <c r="V2" t="n">
-        <v>442784000</v>
+        <v>1006812000</v>
       </c>
       <c r="W2" t="n">
-        <v>132117000</v>
+        <v>281142000</v>
       </c>
       <c r="X2" t="n">
-        <v>310667000</v>
+        <v>725670000</v>
       </c>
       <c r="Y2" t="n">
-        <v>384428000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>8989000</v>
-      </c>
+        <v>598870000</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>171431000</v>
+        <v>279715000</v>
       </c>
       <c r="AB2" t="n">
-        <v>90742000</v>
+        <v>138194000</v>
       </c>
       <c r="AC2" t="n">
-        <v>80689000</v>
+        <v>141521000</v>
       </c>
       <c r="AD2" t="n">
-        <v>40321000</v>
+        <v>74510000</v>
       </c>
       <c r="AE2" t="n">
-        <v>14175000</v>
+        <v>31024000</v>
       </c>
       <c r="AF2" t="n">
-        <v>5633000</v>
+        <v>14179000</v>
       </c>
       <c r="AG2" t="n">
-        <v>20513000</v>
+        <v>29307000</v>
       </c>
       <c r="AH2" t="n">
-        <v>1960167000</v>
+        <v>3022949000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1513268000</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
+        <v>1807091000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
       <c r="AK2" t="n">
-        <v>34086000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
+        <v>13695000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>19891000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>19891000</v>
+      </c>
       <c r="AN2" t="n">
-        <v>1704000</v>
+        <v>2151000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1704000</v>
+        <v>2151000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1128450000</v>
+        <v>1241139000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>731031000</v>
+        <v>804033000</v>
       </c>
       <c r="AR2" t="n">
-        <v>397419000</v>
+        <v>437106000</v>
       </c>
       <c r="AS2" t="n">
-        <v>297107000</v>
+        <v>530215000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-208726000</v>
+        <v>-124512000</v>
       </c>
       <c r="AU2" t="n">
-        <v>505833000</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
+        <v>654727000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
       <c r="AW2" t="n">
-        <v>10509000</v>
+        <v>18095000</v>
       </c>
       <c r="AX2" t="n">
-        <v>26646000</v>
+        <v>22317000</v>
       </c>
       <c r="AY2" t="n">
-        <v>468678000</v>
+        <v>614315000</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>446899000</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
+        <v>1215858000</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>485907000</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>310769000</v>
+      </c>
       <c r="BD2" t="n">
-        <v>1808000</v>
+        <v>2923000</v>
       </c>
       <c r="BE2" t="n">
-        <v>1808000</v>
+        <v>2923000</v>
       </c>
       <c r="BF2" t="n">
-        <v>344779000</v>
+        <v>255887000</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>3401000</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>-412000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>3813000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>100312000</v>
+        <v>156971000</v>
       </c>
       <c r="BK2" t="n">
-        <v>20009000</v>
+        <v>69344000</v>
       </c>
       <c r="BL2" t="n">
-        <v>80303000</v>
+        <v>87627000</v>
       </c>
       <c r="BM2" t="n">
-        <v>80303000</v>
+        <v>87627000</v>
       </c>
     </row>
     <row r="3">
@@ -1824,195 +1832,187 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>123606201</v>
+        <v>127933124</v>
       </c>
       <c r="C4" t="n">
-        <v>123606201</v>
+        <v>127933124</v>
       </c>
       <c r="D4" t="n">
-        <v>779564000</v>
+        <v>311053000</v>
       </c>
       <c r="E4" t="n">
-        <v>1286527000</v>
+        <v>614215000</v>
       </c>
       <c r="F4" t="n">
-        <v>-144426000</v>
+        <v>-390748000</v>
       </c>
       <c r="G4" t="n">
-        <v>1963904000</v>
+        <v>1129058000</v>
       </c>
       <c r="H4" t="n">
-        <v>616988000</v>
+        <v>62471000</v>
       </c>
       <c r="I4" t="n">
-        <v>-144426000</v>
+        <v>-390748000</v>
       </c>
       <c r="J4" t="n">
-        <v>419336000</v>
+        <v>222859000</v>
       </c>
       <c r="K4" t="n">
-        <v>1096713000</v>
+        <v>737702000</v>
       </c>
       <c r="L4" t="n">
-        <v>1822383000</v>
+        <v>1048369000</v>
       </c>
       <c r="M4" t="n">
-        <v>1249743000</v>
+        <v>755949000</v>
       </c>
       <c r="N4" t="n">
-        <v>153030000</v>
+        <v>18247000</v>
       </c>
       <c r="O4" t="n">
-        <v>1096713000</v>
+        <v>737702000</v>
       </c>
       <c r="P4" t="n">
-        <v>42850000</v>
+        <v>44350000</v>
       </c>
       <c r="Q4" t="n">
-        <v>42850000</v>
+        <v>44350000</v>
       </c>
       <c r="R4" t="n">
-        <v>1773206000</v>
+        <v>1204218000</v>
       </c>
       <c r="S4" t="n">
-        <v>1174336000</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
+        <v>819790000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>224189000</v>
+      </c>
       <c r="U4" t="n">
-        <v>167524000</v>
+        <v>152817000</v>
       </c>
       <c r="V4" t="n">
-        <v>1006812000</v>
+        <v>442784000</v>
       </c>
       <c r="W4" t="n">
-        <v>281142000</v>
+        <v>132117000</v>
       </c>
       <c r="X4" t="n">
-        <v>725670000</v>
+        <v>310667000</v>
       </c>
       <c r="Y4" t="n">
-        <v>598870000</v>
-      </c>
-      <c r="Z4" t="inlineStr"/>
+        <v>384428000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>8989000</v>
+      </c>
       <c r="AA4" t="n">
-        <v>279715000</v>
+        <v>171431000</v>
       </c>
       <c r="AB4" t="n">
-        <v>138194000</v>
+        <v>90742000</v>
       </c>
       <c r="AC4" t="n">
-        <v>141521000</v>
+        <v>80689000</v>
       </c>
       <c r="AD4" t="n">
-        <v>74510000</v>
+        <v>40321000</v>
       </c>
       <c r="AE4" t="n">
-        <v>31024000</v>
+        <v>14175000</v>
       </c>
       <c r="AF4" t="n">
-        <v>14179000</v>
+        <v>5633000</v>
       </c>
       <c r="AG4" t="n">
-        <v>29307000</v>
+        <v>20513000</v>
       </c>
       <c r="AH4" t="n">
-        <v>3022949000</v>
+        <v>1960167000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1807091000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
+        <v>1513268000</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>13695000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>19891000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>19891000</v>
-      </c>
+        <v>34086000</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>2151000</v>
+        <v>1704000</v>
       </c>
       <c r="AO4" t="n">
-        <v>2151000</v>
+        <v>1704000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1241139000</v>
+        <v>1128450000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>804033000</v>
+        <v>731031000</v>
       </c>
       <c r="AR4" t="n">
-        <v>437106000</v>
+        <v>397419000</v>
       </c>
       <c r="AS4" t="n">
-        <v>530215000</v>
+        <v>297107000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-124512000</v>
+        <v>-208726000</v>
       </c>
       <c r="AU4" t="n">
-        <v>654727000</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
+        <v>505833000</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
-        <v>18095000</v>
+        <v>10509000</v>
       </c>
       <c r="AX4" t="n">
-        <v>22317000</v>
+        <v>26646000</v>
       </c>
       <c r="AY4" t="n">
-        <v>614315000</v>
+        <v>468678000</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>1215858000</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>485907000</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>310769000</v>
-      </c>
+        <v>446899000</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>2923000</v>
+        <v>1808000</v>
       </c>
       <c r="BE4" t="n">
-        <v>2923000</v>
+        <v>1808000</v>
       </c>
       <c r="BF4" t="n">
-        <v>255887000</v>
+        <v>344779000</v>
       </c>
       <c r="BG4" t="n">
-        <v>3401000</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>-412000</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>3813000</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>156971000</v>
+        <v>100312000</v>
       </c>
       <c r="BK4" t="n">
-        <v>69344000</v>
+        <v>20009000</v>
       </c>
       <c r="BL4" t="n">
-        <v>87627000</v>
+        <v>80303000</v>
       </c>
       <c r="BM4" t="n">
-        <v>87627000</v>
+        <v>80303000</v>
       </c>
     </row>
   </sheetData>
@@ -2283,149 +2283,151 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>46322000</v>
+        <v>80479000</v>
       </c>
       <c r="C2" t="n">
-        <v>-115681000</v>
+        <v>-169095000</v>
       </c>
       <c r="D2" t="n">
-        <v>31623000</v>
+        <v>149235000</v>
       </c>
       <c r="E2" t="n">
-        <v>221207000</v>
+        <v>113745000</v>
       </c>
       <c r="F2" t="n">
-        <v>-36369000</v>
+        <v>-24770000</v>
       </c>
       <c r="G2" t="n">
-        <v>80303000</v>
+        <v>87627000</v>
       </c>
       <c r="H2" t="n">
-        <v>53847000</v>
+        <v>81530000</v>
       </c>
       <c r="I2" t="n">
-        <v>-726000</v>
+        <v>2509000</v>
       </c>
       <c r="J2" t="n">
-        <v>27182000</v>
+        <v>3588000</v>
       </c>
       <c r="K2" t="n">
-        <v>-45027000</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>33453000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>147777000</v>
+      </c>
       <c r="M2" t="n">
-        <v>-45291000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>222472000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>222472000</v>
-      </c>
+        <v>-83057000</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>-1265000</v>
+        <v>113745000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1265000</v>
+        <v>113745000</v>
       </c>
       <c r="R2" t="n">
-        <v>-84058000</v>
+        <v>-19860000</v>
       </c>
       <c r="S2" t="n">
-        <v>-84058000</v>
+        <v>-19860000</v>
       </c>
       <c r="T2" t="n">
-        <v>-115681000</v>
+        <v>-169095000</v>
       </c>
       <c r="U2" t="n">
-        <v>31623000</v>
+        <v>149235000</v>
       </c>
       <c r="V2" t="n">
-        <v>-10482000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+        <v>-135114000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-132522000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>18821000</v>
+      </c>
       <c r="Y2" t="n">
-        <v>25887000</v>
+        <v>-42414000</v>
       </c>
       <c r="Z2" t="n">
-        <v>207719000</v>
+        <v>12118000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-181832000</v>
+        <v>-54532000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>44536000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2424000</v>
+      </c>
       <c r="AD2" t="n">
-        <v>-36369000</v>
+        <v>-23535000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1235000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-36369000</v>
+        <v>-24770000</v>
       </c>
       <c r="AG2" t="n">
-        <v>82691000</v>
+        <v>105249000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-4115000</v>
+        <v>-32965000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1624000</v>
+        <v>7227000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-89054000</v>
+        <v>-63126000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-6396000</v>
+        <v>58561000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-52262000</v>
+        <v>7852000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-10717000</v>
+        <v>17223000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-24609000</v>
+        <v>-106853000</v>
       </c>
       <c r="AO2" t="n">
-        <v>132000</v>
+        <v>-79464000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4798000</v>
+        <v>39555000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>49429000</v>
+        <v>58090000</v>
       </c>
       <c r="AR2" t="n">
-        <v>37263000</v>
+        <v>982000</v>
       </c>
       <c r="AS2" t="n">
-        <v>67950000</v>
+        <v>-3063000</v>
       </c>
       <c r="AT2" t="n">
-        <v>179154000</v>
+        <v>146136000</v>
       </c>
       <c r="AU2" t="n">
-        <v>179154000</v>
+        <v>146136000</v>
       </c>
       <c r="AV2" t="n">
-        <v>3760000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>754000</v>
-      </c>
+        <v>-1762000</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>-60439000</v>
       </c>
       <c r="AY2" t="n">
-        <v>-163769000</v>
+        <v>53409000</v>
       </c>
     </row>
     <row r="3">
@@ -2581,151 +2583,149 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>80479000</v>
+        <v>46322000</v>
       </c>
       <c r="C4" t="n">
-        <v>-169095000</v>
+        <v>-115681000</v>
       </c>
       <c r="D4" t="n">
-        <v>149235000</v>
+        <v>31623000</v>
       </c>
       <c r="E4" t="n">
-        <v>113745000</v>
+        <v>221207000</v>
       </c>
       <c r="F4" t="n">
-        <v>-24770000</v>
+        <v>-36369000</v>
       </c>
       <c r="G4" t="n">
-        <v>87627000</v>
+        <v>80303000</v>
       </c>
       <c r="H4" t="n">
-        <v>81530000</v>
+        <v>53847000</v>
       </c>
       <c r="I4" t="n">
-        <v>2509000</v>
+        <v>-726000</v>
       </c>
       <c r="J4" t="n">
-        <v>3588000</v>
+        <v>27182000</v>
       </c>
       <c r="K4" t="n">
-        <v>33453000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>147777000</v>
-      </c>
+        <v>-45027000</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>-83057000</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+        <v>-45291000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>222472000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>222472000</v>
+      </c>
       <c r="P4" t="n">
-        <v>113745000</v>
+        <v>-1265000</v>
       </c>
       <c r="Q4" t="n">
-        <v>113745000</v>
+        <v>-1265000</v>
       </c>
       <c r="R4" t="n">
-        <v>-19860000</v>
+        <v>-84058000</v>
       </c>
       <c r="S4" t="n">
-        <v>-19860000</v>
+        <v>-84058000</v>
       </c>
       <c r="T4" t="n">
-        <v>-169095000</v>
+        <v>-115681000</v>
       </c>
       <c r="U4" t="n">
-        <v>149235000</v>
+        <v>31623000</v>
       </c>
       <c r="V4" t="n">
-        <v>-135114000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-132522000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>18821000</v>
-      </c>
+        <v>-10482000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>-42414000</v>
+        <v>25887000</v>
       </c>
       <c r="Z4" t="n">
-        <v>12118000</v>
+        <v>207719000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-54532000</v>
+        <v>-181832000</v>
       </c>
       <c r="AB4" t="n">
-        <v>44536000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2424000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>-23535000</v>
+        <v>-36369000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1235000</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-24770000</v>
+        <v>-36369000</v>
       </c>
       <c r="AG4" t="n">
-        <v>105249000</v>
+        <v>82691000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-32965000</v>
+        <v>-4115000</v>
       </c>
       <c r="AI4" t="n">
-        <v>7227000</v>
+        <v>1624000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-63126000</v>
+        <v>-89054000</v>
       </c>
       <c r="AK4" t="n">
-        <v>58561000</v>
+        <v>-6396000</v>
       </c>
       <c r="AL4" t="n">
-        <v>7852000</v>
+        <v>-52262000</v>
       </c>
       <c r="AM4" t="n">
-        <v>17223000</v>
+        <v>-10717000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-106853000</v>
+        <v>-24609000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-79464000</v>
+        <v>132000</v>
       </c>
       <c r="AP4" t="n">
-        <v>39555000</v>
+        <v>4798000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>58090000</v>
+        <v>49429000</v>
       </c>
       <c r="AR4" t="n">
-        <v>982000</v>
+        <v>37263000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-3063000</v>
+        <v>67950000</v>
       </c>
       <c r="AT4" t="n">
-        <v>146136000</v>
+        <v>179154000</v>
       </c>
       <c r="AU4" t="n">
-        <v>146136000</v>
+        <v>179154000</v>
       </c>
       <c r="AV4" t="n">
-        <v>-1762000</v>
-      </c>
-      <c r="AW4" t="inlineStr"/>
+        <v>3760000</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>754000</v>
+      </c>
       <c r="AX4" t="n">
-        <v>-60439000</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>53409000</v>
+        <v>-163769000</v>
       </c>
     </row>
   </sheetData>
@@ -3275,192 +3275,192 @@
       </c>
       <c r="DC1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
       <c r="EO1" t="inlineStr">
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.291</v>
+        <v>0.25</v>
       </c>
       <c r="AF2" t="n">
         <v>43.666664</v>
@@ -3729,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BX2" t="n">
         <v>0.023227</v>
@@ -3842,143 +3842,143 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DD2" t="n">
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>AIDIGONG</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DE2" t="n">
+        <v>1740102127</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>finmb_7658035</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DJ2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="n">
         <v>-0.75758404</v>
       </c>
-      <c r="DE2" t="n">
+      <c r="DN2" t="n">
         <v>1.31</v>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DO2" t="inlineStr">
         <is>
           <t>PREPRE</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>AIDIGONG</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1075080600000</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.01000011</v>
+      </c>
+      <c r="DS2" t="inlineStr">
         <is>
           <t>Aidigong Maternal &amp; Child Health Limited</t>
         </is>
       </c>
-      <c r="DI2" t="n">
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>1.32 - 1.32</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>1.31 - 1.32</t>
+        </is>
+      </c>
+      <c r="DZ2" t="n">
         <v>-0.01000011</v>
       </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>1.32 - 1.32</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>1.31 - 1.32</t>
-        </is>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.01000011</v>
-      </c>
-      <c r="DQ2" t="n">
+      <c r="EA2" t="n">
         <v>-0.00757584</v>
       </c>
-      <c r="DR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS2" t="n">
+      <c r="EB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC2" t="n">
         <v>1756378740</v>
       </c>
-      <c r="DT2" t="n">
+      <c r="ED2" t="n">
         <v>1756728000</v>
       </c>
-      <c r="DU2" t="b">
+      <c r="EE2" t="b">
         <v>1</v>
       </c>
-      <c r="DV2" t="n">
+      <c r="EF2" t="n">
         <v>-1.52</v>
       </c>
-      <c r="DW2" t="n">
+      <c r="EG2" t="n">
         <v>0.03</v>
       </c>
-      <c r="DX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB2" t="n">
+      <c r="EH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL2" t="n">
         <v>15</v>
       </c>
-      <c r="EC2" t="n">
+      <c r="EM2" t="n">
         <v>15</v>
       </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EE2" t="n">
-        <v>1740102127</v>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>finmb_7658035</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="EJ2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EM2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>1075080600000</v>
+      <c r="EN2" t="b">
+        <v>0</v>
       </c>
       <c r="EO2" t="inlineStr"/>
     </row>
